--- a/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
+++ b/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
   <si>
     <t xml:space="preserve">:table Loadout</t>
   </si>
@@ -141,6 +141,33 @@
   </si>
   <si>
     <t xml:space="preserve">third</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Bonuses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A multi-row group whose members a schema file declares.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus[].StatId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which stat it raises.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus[].Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By how much.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
   </si>
 </sst>
 </file>
@@ -185,7 +212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:K9"/>
+  <dimension ref="B2:K22"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -411,6 +438,136 @@
         <v>41</v>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
+++ b/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
   <si>
     <t xml:space="preserve">:table Loadout</t>
   </si>
@@ -212,7 +212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:K22"/>
+  <dimension ref="B2:K21"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -537,34 +537,23 @@
     </row>
     <row r="20">
       <c r="C20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" t="s">
         <v>30</v>
       </c>
     </row>

--- a/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
+++ b/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
   <si>
     <t xml:space="preserve">:table Loadout</t>
   </si>
@@ -168,6 +168,30 @@
   </si>
   <si>
     <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Chest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A second table whose group the same declaration types.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prize.ItemId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prize.Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prize.Icon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
   </si>
 </sst>
 </file>
@@ -212,7 +236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:K21"/>
+  <dimension ref="B2:K30"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -557,6 +581,110 @@
         <v>30</v>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
+++ b/test/fixtures/xlsx/declared-expanded/declared-expanded.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Grade</t>
   </si>
   <si>
-    <t xml:space="preserve">Element</t>
+    <t xml:space="preserve">Affinity</t>
   </si>
   <si>
     <t xml:space="preserve">an enum the schema file declares</t>
